--- a/DB_Iglesia/RevisionCanciones.xlsx
+++ b/DB_Iglesia/RevisionCanciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\Proyectos\himnario-pwa\DB_Iglesia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9383A28B-7454-4DBD-A6A9-453DB3391117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C147CF-7C1E-42AC-B3BE-6104972877BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{A883B1C6-0CF1-4C98-8DA4-043FDBBF6337}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{A883B1C6-0CF1-4C98-8DA4-043FDBBF6337}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="290">
   <si>
     <t>HIMNOS</t>
   </si>
@@ -182,9 +182,6 @@
     <t>Cristo es la peña de Horeb</t>
   </si>
   <si>
-    <t>ADORACION BOLERO</t>
-  </si>
-  <si>
     <t>Cristo es mío</t>
   </si>
   <si>
@@ -212,9 +209,6 @@
     <t>Cuando allá se pase lista</t>
   </si>
   <si>
-    <t>HIMNO ALABANZA</t>
-  </si>
-  <si>
     <t>Cuando cristo vino</t>
   </si>
   <si>
@@ -287,9 +281,6 @@
     <t>El aleluya</t>
   </si>
   <si>
-    <t>COUNTRY</t>
-  </si>
-  <si>
     <t>El amor de Dios</t>
   </si>
   <si>
@@ -527,9 +518,6 @@
     <t>La oracion del profeta</t>
   </si>
   <si>
-    <t>SWING</t>
-  </si>
-  <si>
     <t>La paloma</t>
   </si>
   <si>
@@ -542,9 +530,6 @@
     <t>La sangre de cristo tien poder</t>
   </si>
   <si>
-    <t>ALANAZA</t>
-  </si>
-  <si>
     <t>La trompeta esta sonando</t>
   </si>
   <si>
@@ -596,9 +581,6 @@
     <t>Mas alla del sol</t>
   </si>
   <si>
-    <t>ADORACION FUNERAL</t>
-  </si>
-  <si>
     <t>Me ha tocado</t>
   </si>
   <si>
@@ -759,6 +741,174 @@
   </si>
   <si>
     <t>Solamnete en cristo</t>
+  </si>
+  <si>
+    <t>BOLERO</t>
+  </si>
+  <si>
+    <t>Solo de jesus la sangre</t>
+  </si>
+  <si>
+    <t>Solo Dios hace al hombre feliz</t>
+  </si>
+  <si>
+    <t>Solo el poder de Dios</t>
+  </si>
+  <si>
+    <t>Soy de el</t>
+  </si>
+  <si>
+    <t>Soy feliz</t>
+  </si>
+  <si>
+    <t>Soy libertado</t>
+  </si>
+  <si>
+    <t>Soy yo soldado de jesus</t>
+  </si>
+  <si>
+    <t>Sublime gracia</t>
+  </si>
+  <si>
+    <t>Tan solo cree</t>
+  </si>
+  <si>
+    <t>Te alabo</t>
+  </si>
+  <si>
+    <t>Te exaltare mi Dios mi rey</t>
+  </si>
+  <si>
+    <t>Tengo la seguridad</t>
+  </si>
+  <si>
+    <t>Tierra de palestina</t>
+  </si>
+  <si>
+    <t>Todo a cristo yo me rindo</t>
+  </si>
+  <si>
+    <t>Todo en todo es jesucristo</t>
+  </si>
+  <si>
+    <t>Todo lo que respire alabe a jehova</t>
+  </si>
+  <si>
+    <t>Toma por favor mi mano</t>
+  </si>
+  <si>
+    <t>Tres cosas quiero yo</t>
+  </si>
+  <si>
+    <t>Tu fidelidad es grande</t>
+  </si>
+  <si>
+    <t>Tus espinas daran rosas</t>
+  </si>
+  <si>
+    <t>Trigo soy</t>
+  </si>
+  <si>
+    <t>Un dia cristo volvera</t>
+  </si>
+  <si>
+    <t>Una gota de tu sangre</t>
+  </si>
+  <si>
+    <t>Una mirada de fe</t>
+  </si>
+  <si>
+    <t>Unos brazos humildes</t>
+  </si>
+  <si>
+    <t>Vamos alabar al señor</t>
+  </si>
+  <si>
+    <t>Vamos escalando peldaños</t>
+  </si>
+  <si>
+    <t>Ven a la luz</t>
+  </si>
+  <si>
+    <t>Ven ven ven espiritu divino</t>
+  </si>
+  <si>
+    <t>Victoria en cristo</t>
+  </si>
+  <si>
+    <t>Vida nueva encontre</t>
+  </si>
+  <si>
+    <t>Vine a adorar a Dios</t>
+  </si>
+  <si>
+    <t>Vision patoral</t>
+  </si>
+  <si>
+    <t>Vive Dios</t>
+  </si>
+  <si>
+    <t>Y los fariseos</t>
+  </si>
+  <si>
+    <t>Ya viene Cristo</t>
+  </si>
+  <si>
+    <t>Yo andaba en el mundo sin salvacion</t>
+  </si>
+  <si>
+    <t>Yo espero la mañana</t>
+  </si>
+  <si>
+    <t>Yo le alabo con el corazon</t>
+  </si>
+  <si>
+    <t>Yo le amo</t>
+  </si>
+  <si>
+    <t>Yo me gozo</t>
+  </si>
+  <si>
+    <t>Yo presiento</t>
+  </si>
+  <si>
+    <t>Yo quiero andar las calles de oro</t>
+  </si>
+  <si>
+    <t>Yo quiero mas</t>
+  </si>
+  <si>
+    <t>Yo quiero ser Señor amado</t>
+  </si>
+  <si>
+    <t>Yo soy testigo del poder de Dios</t>
+  </si>
+  <si>
+    <t>Yo tengo gozo en mi alma</t>
+  </si>
+  <si>
+    <t>Yo tengo paz y gozo</t>
+  </si>
+  <si>
+    <t>Yo tengo un abogado</t>
+  </si>
+  <si>
+    <t>Yo tengo un amigo</t>
+  </si>
+  <si>
+    <t>Yo vivo Señor porque tu vives</t>
+  </si>
+  <si>
+    <t>Clamando estoy</t>
+  </si>
+  <si>
+    <t>Aqui se sinete la presencia de Dios</t>
+  </si>
+  <si>
+    <t>En Arizona</t>
+  </si>
+  <si>
+    <t>EDGARDO</t>
   </si>
 </sst>
 </file>
@@ -1227,15 +1377,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFFAD3AD-3141-4DD4-85D5-8961B77DBF3E}">
-  <dimension ref="A1:C213"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C267"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.6640625" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="31.21875" customWidth="1"/>
+    <col min="1" max="1" width="37.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="42.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1246,7 +1396,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -1257,7 +1407,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -1268,7 +1418,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1279,7 +1429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1290,7 +1440,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -1301,7 +1451,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -1312,7 +1462,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
@@ -1323,7 +1473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -1334,7 +1484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -1345,7 +1495,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
@@ -1356,7 +1506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
@@ -1367,7 +1517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
@@ -1378,7 +1528,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>21</v>
       </c>
@@ -1389,7 +1539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>22</v>
       </c>
@@ -1400,7 +1550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>23</v>
       </c>
@@ -1411,7 +1561,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>24</v>
       </c>
@@ -1422,7 +1572,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>26</v>
       </c>
@@ -1433,7 +1583,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
@@ -1444,7 +1594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
@@ -1455,7 +1605,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>30</v>
       </c>
@@ -1466,7 +1616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>31</v>
       </c>
@@ -1477,7 +1627,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>33</v>
       </c>
@@ -1488,18 +1638,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>35</v>
       </c>
@@ -1510,18 +1660,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>37</v>
       </c>
@@ -1532,7 +1682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
@@ -1543,7 +1693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>40</v>
       </c>
@@ -1554,7 +1704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>41</v>
       </c>
@@ -1565,7 +1715,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>42</v>
       </c>
@@ -1576,7 +1726,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>43</v>
       </c>
@@ -1587,7 +1737,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>44</v>
       </c>
@@ -1598,7 +1748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>45</v>
       </c>
@@ -1609,7 +1759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>46</v>
       </c>
@@ -1617,122 +1767,122 @@
         <v>32</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="5" t="s">
+      <c r="B36" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="3" t="s">
+      <c r="B37" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
+      <c r="B38" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="C38" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="5" t="s">
+      <c r="B39" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
+      <c r="B40" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="3" t="s">
+      <c r="B41" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="3" t="s">
+      <c r="B42" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="3" t="s">
+      <c r="B43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="B44" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="3" t="s">
+      <c r="B45" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>25</v>
@@ -1741,86 +1891,86 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="3" t="s">
+      <c r="B49" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="9" t="s">
+      <c r="B50" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="3" t="s">
+      <c r="B51" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="5" t="s">
+      <c r="B52" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="3" t="s">
+      <c r="B53" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>10</v>
@@ -1829,86 +1979,86 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B56" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="3" t="s">
+      <c r="B57" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B56" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="3" t="s">
+      <c r="B58" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="3" t="s">
+      <c r="C58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B59" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="3" t="s">
+      <c r="B60" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B59" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="3" t="s">
+      <c r="B61" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="3" t="s">
+      <c r="C61" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>10</v>
@@ -1917,218 +2067,218 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B63" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="3" t="s">
+      <c r="B65" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B64" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C64" s="3" t="s">
+      <c r="B66" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="3" t="s">
+      <c r="B67" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B65" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="3" t="s">
+      <c r="B68" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B66" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="3" t="s">
+      <c r="B69" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B67" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="5" t="s">
+      <c r="C69" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B68" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="3" t="s">
+      <c r="B70" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B71" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="5" t="s">
+      <c r="B72" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B70" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="9" t="s">
+      <c r="B73" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B71" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="3" t="s">
+      <c r="B74" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B72" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="3" t="s">
+      <c r="B75" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B73" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="3" t="s">
+      <c r="B76" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B74" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="3" t="s">
+      <c r="B77" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B75" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="3" t="s">
+      <c r="B78" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B76" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="3" t="s">
+      <c r="B79" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B77" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="3" t="s">
+      <c r="B80" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B78" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="3" t="s">
+      <c r="C80" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B79" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="3" t="s">
+      <c r="B81" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="10" t="s">
-        <v>102</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>25</v>
@@ -2137,9 +2287,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>27</v>
@@ -2148,20 +2298,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>32</v>
@@ -2170,75 +2320,75 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B86" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="3" t="s">
+      <c r="B89" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B87" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="3" t="s">
+      <c r="B90" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B88" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="3" t="s">
+      <c r="B91" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>10</v>
@@ -2247,75 +2397,75 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="B94" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="3" t="s">
+      <c r="B97" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="3" t="s">
+      <c r="B98" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B97" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C97" s="13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="5" t="s">
-        <v>119</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>25</v>
@@ -2324,9 +2474,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>32</v>
@@ -2335,9 +2485,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>7</v>
@@ -2346,9 +2496,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>32</v>
@@ -2357,9 +2507,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>7</v>
@@ -2368,9 +2518,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>7</v>
@@ -2379,9 +2529,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>10</v>
@@ -2390,9 +2540,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>25</v>
@@ -2401,9 +2551,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>7</v>
@@ -2412,20 +2562,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>32</v>
@@ -2434,9 +2584,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>10</v>
@@ -2445,53 +2595,53 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B111" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="3" t="s">
+      <c r="B113" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B114" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>10</v>
@@ -2500,31 +2650,31 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>10</v>
@@ -2533,42 +2683,42 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>10</v>
@@ -2577,9 +2727,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>39</v>
@@ -2588,9 +2738,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>4</v>
@@ -2599,9 +2749,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>32</v>
@@ -2610,9 +2760,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>4</v>
@@ -2621,9 +2771,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>32</v>
@@ -2632,42 +2782,42 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>39</v>
@@ -2676,9 +2826,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>4</v>
@@ -2687,20 +2837,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>25</v>
@@ -2709,9 +2859,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>10</v>
@@ -2720,163 +2870,163 @@
         <v>8</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B136" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C136" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="5" t="s">
+      <c r="B139" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B137" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="3" t="s">
+      <c r="B140" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B138" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="3" t="s">
+      <c r="B141" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B139" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="3" t="s">
+      <c r="B142" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C142" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B140" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C140" s="3" t="s">
+    </row>
+    <row r="143" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="3" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="5" t="s">
+      <c r="B143" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B141" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="3" t="s">
+      <c r="B144" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B142" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C142" s="3" t="s">
+      <c r="B145" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="3" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="3" t="s">
+      <c r="B146" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B143" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C143" s="3" t="s">
+      <c r="B147" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="3" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="3" t="s">
+      <c r="B148" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B144" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="3" t="s">
+      <c r="B149" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C146" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>10</v>
@@ -2885,20 +3035,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>4</v>
@@ -2907,20 +3057,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>4</v>
@@ -2929,9 +3079,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>25</v>
@@ -2940,9 +3090,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>10</v>
@@ -2951,163 +3101,163 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B157" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="3" t="s">
+      <c r="B162" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B158" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="3" t="s">
+      <c r="B163" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B159" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="3" t="s">
+      <c r="B164" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B160" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C160" s="3" t="s">
+      <c r="B165" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="3" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="3" t="s">
+      <c r="B166" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B161" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="3" t="s">
+      <c r="B167" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B162" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="3" t="s">
+      <c r="B168" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B163" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="3" t="s">
+      <c r="B169" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B164" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C164" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="3" t="s">
+      <c r="B170" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C166" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C167" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C168" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C169" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C170" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A171" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>10</v>
@@ -3116,9 +3266,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>4</v>
@@ -3127,31 +3277,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>10</v>
@@ -3160,9 +3310,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>10</v>
@@ -3171,9 +3321,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>4</v>
@@ -3182,20 +3332,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>27</v>
@@ -3204,9 +3354,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>25</v>
@@ -3215,20 +3365,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>25</v>
@@ -3237,97 +3387,97 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C183" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="3" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A184" s="3" t="s">
-        <v>210</v>
-      </c>
       <c r="B184" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>7</v>
@@ -3336,20 +3486,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B193" s="4" t="s">
         <v>7</v>
@@ -3358,20 +3508,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B195" s="4" t="s">
         <v>10</v>
@@ -3380,9 +3530,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>7</v>
@@ -3391,9 +3541,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B197" s="4" t="s">
         <v>39</v>
@@ -3402,20 +3552,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B199" s="4" t="s">
         <v>25</v>
@@ -3424,20 +3574,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B200" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B201" s="4" t="s">
         <v>7</v>
@@ -3446,9 +3596,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B202" s="4" t="s">
         <v>27</v>
@@ -3457,20 +3607,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B203" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B204" s="4" t="s">
         <v>27</v>
@@ -3479,20 +3629,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B205" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B206" s="4" t="s">
         <v>25</v>
@@ -3501,9 +3651,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B207" s="4" t="s">
         <v>7</v>
@@ -3512,9 +3662,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B208" s="4" t="s">
         <v>7</v>
@@ -3523,9 +3673,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B209" s="4" t="s">
         <v>10</v>
@@ -3534,9 +3684,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>27</v>
@@ -3545,9 +3695,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B211" s="4" t="s">
         <v>10</v>
@@ -3556,22 +3706,620 @@
         <v>8</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B212" s="3"/>
-      <c r="C212" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A213" s="3" t="s">
+      <c r="B217" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B213" s="3"/>
-      <c r="C213" s="3" t="s">
-        <v>5</v>
+      <c r="B218" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A221" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A222" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A223" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A224" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A237" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A238" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A242" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A243" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A246" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A248" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A251" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A252" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A256" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A258" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A261" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A262" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A263" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A264" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B264" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A265" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B265" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A266" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A267" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>

--- a/DB_Iglesia/RevisionCanciones.xlsx
+++ b/DB_Iglesia/RevisionCanciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\Proyectos\himnario-pwa\DB_Iglesia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C147CF-7C1E-42AC-B3BE-6104972877BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47386E0-A3BD-4F5C-99C8-3409DA66B3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{A883B1C6-0CF1-4C98-8DA4-043FDBBF6337}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="528">
   <si>
     <t>HIMNOS</t>
   </si>
@@ -909,13 +909,738 @@
   </si>
   <si>
     <t>EDGARDO</t>
+  </si>
+  <si>
+    <t>Bendito sea jehová mi roca</t>
+  </si>
+  <si>
+    <t>Digno eres señor</t>
+  </si>
+  <si>
+    <t>Dilo a Cristo</t>
+  </si>
+  <si>
+    <t>Dulce Comunión</t>
+  </si>
+  <si>
+    <t>El Rapto</t>
+  </si>
+  <si>
+    <t>Es J C jehová la roca </t>
+  </si>
+  <si>
+    <t>Escogido fui de Dios en el amado</t>
+  </si>
+  <si>
+    <t>Grande gozo hay en mi alma hoy</t>
+  </si>
+  <si>
+    <t>Háblame más de Cristo</t>
+  </si>
+  <si>
+    <t>Lo entenderemos todo más allá</t>
+  </si>
+  <si>
+    <t>Mirad bendecid a Jehová</t>
+  </si>
+  <si>
+    <t>No hay Dios tan grande como tu</t>
+  </si>
+  <si>
+    <t>Oh yo quiero andar con cristo</t>
+  </si>
+  <si>
+    <t>Resucito la nueva edad</t>
+  </si>
+  <si>
+    <t>Si en verdad eres salvo</t>
+  </si>
+  <si>
+    <t>Todo lo que respire</t>
+  </si>
+  <si>
+    <t>Un día cristo volverá</t>
+  </si>
+  <si>
+    <t>Yo siento gozo en mi alma</t>
+  </si>
+  <si>
+    <t>Vida nueva encontré</t>
+  </si>
+  <si>
+    <t>DO</t>
+  </si>
+  <si>
+    <t>|</t>
+  </si>
+  <si>
+    <t>Alabare a Jehová</t>
+  </si>
+  <si>
+    <t>Caminando voy para Canaán</t>
+  </si>
+  <si>
+    <t>Jacob lucho con el ángel</t>
+  </si>
+  <si>
+    <t>Mi Dios en un carruaje</t>
+  </si>
+  <si>
+    <t>Cristo es la roca de poder</t>
+  </si>
+  <si>
+    <t>El día llegó</t>
+  </si>
+  <si>
+    <t>Vamos subiendo una escalera</t>
+  </si>
+  <si>
+    <t>RE</t>
+  </si>
+  <si>
+    <t>A Jesucristo ven sin tardad</t>
+  </si>
+  <si>
+    <t>Hay poder en Jesús</t>
+  </si>
+  <si>
+    <t>Las promesas de Jesús</t>
+  </si>
+  <si>
+    <t>Todo en todo es Jesucristo</t>
+  </si>
+  <si>
+    <t>Ven, ven, ven Espíritu Divino</t>
+  </si>
+  <si>
+    <t>Vengan a cenar</t>
+  </si>
+  <si>
+    <t>Edifique mi casa</t>
+  </si>
+  <si>
+    <t>Alabad a Dios con alegría </t>
+  </si>
+  <si>
+    <t>La puerta de los gentiles</t>
+  </si>
+  <si>
+    <t>RE-</t>
+  </si>
+  <si>
+    <t>Hay victoria en mi Jesús</t>
+  </si>
+  <si>
+    <t>El poderoso de Israel</t>
+  </si>
+  <si>
+    <t>Jesucristo es tan grande</t>
+  </si>
+  <si>
+    <t>Salmo 66 aclamad a Dios</t>
+  </si>
+  <si>
+    <t>Satúrame</t>
+  </si>
+  <si>
+    <t>Señor llévame a tus atrios</t>
+  </si>
+  <si>
+    <t>Te exaltare</t>
+  </si>
+  <si>
+    <t>Amarte solo a ti</t>
+  </si>
+  <si>
+    <t>Ebenum Shalom</t>
+  </si>
+  <si>
+    <t>Si no hubiera sido por el señor</t>
+  </si>
+  <si>
+    <t>Dios nos trajo hasta aquí</t>
+  </si>
+  <si>
+    <t>LA-</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>Como el arca de Noé</t>
+  </si>
+  <si>
+    <t>Dios está aquí que precioso es</t>
+  </si>
+  <si>
+    <t>Donde está el Espíritu de Dios</t>
+  </si>
+  <si>
+    <t>La gloriosa aparición</t>
+  </si>
+  <si>
+    <t>Libertad o que buena</t>
+  </si>
+  <si>
+    <t>Libre, tú me hiciste libre</t>
+  </si>
+  <si>
+    <t>Manda el fuego</t>
+  </si>
+  <si>
+    <t>Poder maravillosos poder</t>
+  </si>
+  <si>
+    <t>Seguiré a mi Jesús  (soy bautizado)</t>
+  </si>
+  <si>
+    <t>Sí, soy yo, soy el templo</t>
+  </si>
+  <si>
+    <t>Solamente en cristo</t>
+  </si>
+  <si>
+    <t>Ya viene cristo</t>
+  </si>
+  <si>
+    <t>Yo vivo señor porque tú vives</t>
+  </si>
+  <si>
+    <t>He Decidido seguir a Cristo</t>
+  </si>
+  <si>
+    <t>Tengo un Dios poderoso</t>
+  </si>
+  <si>
+    <t>Yo veré la gloria de jehová</t>
+  </si>
+  <si>
+    <t>FA</t>
+  </si>
+  <si>
+    <t>Hoy dia vi</t>
+  </si>
+  <si>
+    <t>FA#-</t>
+  </si>
+  <si>
+    <t>Aunque un ejercito</t>
+  </si>
+  <si>
+    <t>SOL</t>
+  </si>
+  <si>
+    <t>Cuando cristo vino a mi corazón</t>
+  </si>
+  <si>
+    <t>Demos gracias al señor</t>
+  </si>
+  <si>
+    <t>En el aposento alto</t>
+  </si>
+  <si>
+    <t>Galardón</t>
+  </si>
+  <si>
+    <t>Halle un buen amigo</t>
+  </si>
+  <si>
+    <t>Qué bonito es</t>
+  </si>
+  <si>
+    <t>Tal como el sirvo brama (salmo 42)</t>
+  </si>
+  <si>
+    <t>Allá en el cielo todos cantan aleluya</t>
+  </si>
+  <si>
+    <t>Bendita sea la gracia</t>
+  </si>
+  <si>
+    <t>Carácter no es un Don</t>
+  </si>
+  <si>
+    <t>El cielo es el trono de mi Dios</t>
+  </si>
+  <si>
+    <t>Eres limpio en la sangre </t>
+  </si>
+  <si>
+    <t>Espíritu de Dios desciende sobre mi</t>
+  </si>
+  <si>
+    <t>Regalo de Dios</t>
+  </si>
+  <si>
+    <t>Vuelvo a mi hogar</t>
+  </si>
+  <si>
+    <t>Ya viene la mañana </t>
+  </si>
+  <si>
+    <t>Yo quiero andar con Cristo</t>
+  </si>
+  <si>
+    <t>LA</t>
+  </si>
+  <si>
+    <t>El Espíritu de Dios está en este lugar</t>
+  </si>
+  <si>
+    <t>El me levantara</t>
+  </si>
+  <si>
+    <t>La mejor oración es amar</t>
+  </si>
+  <si>
+    <t>La oración del profeta</t>
+  </si>
+  <si>
+    <t>Pecador ven a cristo Jesús</t>
+  </si>
+  <si>
+    <t>Puedo oir tu voz llamando</t>
+  </si>
+  <si>
+    <t>Renuévame</t>
+  </si>
+  <si>
+    <t>Tu fidelidad</t>
+  </si>
+  <si>
+    <t>Yo quiero ser señor amado</t>
+  </si>
+  <si>
+    <t>Esa sangre que vertió Jesús</t>
+  </si>
+  <si>
+    <t>Mi día en el calvario</t>
+  </si>
+  <si>
+    <t>Mi fe en el</t>
+  </si>
+  <si>
+    <t>Tierno salvador</t>
+  </si>
+  <si>
+    <t>Volverá, yo sé que volverá</t>
+  </si>
+  <si>
+    <t>Yo sé que fue la sangre</t>
+  </si>
+  <si>
+    <t>De maña oirás mi voz</t>
+  </si>
+  <si>
+    <t>Tengo una razón</t>
+  </si>
+  <si>
+    <t>Dejo el mundo sigo a Cristo</t>
+  </si>
+  <si>
+    <t>El gran medico</t>
+  </si>
+  <si>
+    <t>Has lo que quieras de mi señor</t>
+  </si>
+  <si>
+    <t>Jesús pronto volverá</t>
+  </si>
+  <si>
+    <t>No puedo vivir sin Ud. mi hermano</t>
+  </si>
+  <si>
+    <t>Quiero cantar una linda canción</t>
+  </si>
+  <si>
+    <t>Te adoro buen salvador</t>
+  </si>
+  <si>
+    <t>Toma por favor mi mano señor</t>
+  </si>
+  <si>
+    <t>Día tan grande</t>
+  </si>
+  <si>
+    <t>Señor quien entrara</t>
+  </si>
+  <si>
+    <t>Un día a la vez</t>
+  </si>
+  <si>
+    <t>SOL-</t>
+  </si>
+  <si>
+    <t>En el principio</t>
+  </si>
+  <si>
+    <t>Este avivamiento</t>
+  </si>
+  <si>
+    <t>Grandes y maravillosas</t>
+  </si>
+  <si>
+    <t>Mirad cuan bueno   (salmo 133)</t>
+  </si>
+  <si>
+    <t>Digno es de alabar</t>
+  </si>
+  <si>
+    <t>Hay victoria</t>
+  </si>
+  <si>
+    <t>La ciudad</t>
+  </si>
+  <si>
+    <t>Oh Jerusalén</t>
+  </si>
+  <si>
+    <t>Pandero y danza</t>
+  </si>
+  <si>
+    <t>Por eso yo canto  ( allí no habrá)</t>
+  </si>
+  <si>
+    <t>Si alguien me pregunta</t>
+  </si>
+  <si>
+    <t>Te alabare, te alabare</t>
+  </si>
+  <si>
+    <t>Venid aclamemos a jehová</t>
+  </si>
+  <si>
+    <t>Bajo de la sangre de expiación</t>
+  </si>
+  <si>
+    <t>Me sigo enamorando</t>
+  </si>
+  <si>
+    <t>Cuando los santos</t>
+  </si>
+  <si>
+    <t>Da la luz</t>
+  </si>
+  <si>
+    <t>Desciende aquí Jesús</t>
+  </si>
+  <si>
+    <t>Dios me santifico</t>
+  </si>
+  <si>
+    <t>El es el gran yo soy</t>
+  </si>
+  <si>
+    <t>Esta sonando la séptima trompeta</t>
+  </si>
+  <si>
+    <t>Estamos de fiesta con jesus</t>
+  </si>
+  <si>
+    <t>Firme y adelante</t>
+  </si>
+  <si>
+    <t>Haz tu casa sobre la roca</t>
+  </si>
+  <si>
+    <t>Más allá de la cortina del tiempo</t>
+  </si>
+  <si>
+    <t>Vamos a alabar al señor</t>
+  </si>
+  <si>
+    <t>Yo le alabo con el corazón</t>
+  </si>
+  <si>
+    <t>Yo tengo un amigo que me ama</t>
+  </si>
+  <si>
+    <t>Es la sangre que vertió Jesús</t>
+  </si>
+  <si>
+    <t>Hay un canto nuevo en mi ser</t>
+  </si>
+  <si>
+    <t>Mi Dios es real</t>
+  </si>
+  <si>
+    <t>Porque yo creo en Dios</t>
+  </si>
+  <si>
+    <t>Soy yo soldado de la cruz</t>
+  </si>
+  <si>
+    <t>Abre mis ojos </t>
+  </si>
+  <si>
+    <t>Dejo el mundo y sigo a cristo</t>
+  </si>
+  <si>
+    <t>En momentos así</t>
+  </si>
+  <si>
+    <t>Hay momentos que las palabras</t>
+  </si>
+  <si>
+    <t>Hay momentos tan especiales</t>
+  </si>
+  <si>
+    <t>Lo divino</t>
+  </si>
+  <si>
+    <t>Más allá del sol</t>
+  </si>
+  <si>
+    <t>Mi pastor es Jesús</t>
+  </si>
+  <si>
+    <t>Quien entrara</t>
+  </si>
+  <si>
+    <t>Yo quiero más y más de cristo</t>
+  </si>
+  <si>
+    <t>que SOL</t>
+  </si>
+  <si>
+    <t>Aleluya, aleluya... Gloria a Dios</t>
+  </si>
+  <si>
+    <t>Anhelo pronto ir a mi hogar</t>
+  </si>
+  <si>
+    <t>Él es mi paz</t>
+  </si>
+  <si>
+    <t>El momento más oscuro de la noche</t>
+  </si>
+  <si>
+    <t>El que habita a abrigo(salmo 91)</t>
+  </si>
+  <si>
+    <t>Fue el gran amor de Dios</t>
+  </si>
+  <si>
+    <t>Le amo</t>
+  </si>
+  <si>
+    <t>Lléname señor</t>
+  </si>
+  <si>
+    <t>Mi fe en Él</t>
+  </si>
+  <si>
+    <t>Que linda es la fe</t>
+  </si>
+  <si>
+    <t>Segará</t>
+  </si>
+  <si>
+    <t>Señor capacítame</t>
+  </si>
+  <si>
+    <t>Si tú hablas con Dios</t>
+  </si>
+  <si>
+    <t>Tu misericordia</t>
+  </si>
+  <si>
+    <t>Yo quiero más de ti</t>
+  </si>
+  <si>
+    <t>Basta que me toques señor</t>
+  </si>
+  <si>
+    <t>Cordero</t>
+  </si>
+  <si>
+    <t>El Jordán solo no cruzaré</t>
+  </si>
+  <si>
+    <t>Entra en la presencia</t>
+  </si>
+  <si>
+    <t>Fluirán como ríos</t>
+  </si>
+  <si>
+    <t>La cruz de Jesús </t>
+  </si>
+  <si>
+    <t>Todo a Cristo yo me rindo</t>
+  </si>
+  <si>
+    <t>Vine a adorar Dios</t>
+  </si>
+  <si>
+    <t>Digno de gloria</t>
+  </si>
+  <si>
+    <t>Santo, santo, santo señor de gloria</t>
+  </si>
+  <si>
+    <t>Si le adoramos</t>
+  </si>
+  <si>
+    <t>En mi debilidad</t>
+  </si>
+  <si>
+    <t>Entenderemos nuestras angustias</t>
+  </si>
+  <si>
+    <t>Mi nuevo efesios</t>
+  </si>
+  <si>
+    <t>Señor, quiero regresar</t>
+  </si>
+  <si>
+    <t>El es mi protector</t>
+  </si>
+  <si>
+    <t>MI-</t>
+  </si>
+  <si>
+    <t>Espíritu de Dios </t>
+  </si>
+  <si>
+    <t>Torre fuerte es el nombre del señor</t>
+  </si>
+  <si>
+    <t>Cuando el pueblo del señor </t>
+  </si>
+  <si>
+    <t>Esta es la iglesia del señor</t>
+  </si>
+  <si>
+    <t>Gocémonos y alegrémonos</t>
+  </si>
+  <si>
+    <t>Los que esperan en jehová</t>
+  </si>
+  <si>
+    <t>Pon aceite en mi lámpara</t>
+  </si>
+  <si>
+    <t>Pronto vendrá el señor</t>
+  </si>
+  <si>
+    <t>Santo, santo, decían los querubines</t>
+  </si>
+  <si>
+    <t>Allí no abre tristeza ni llanto</t>
+  </si>
+  <si>
+    <t>Aquí se siente la presencia de Dios</t>
+  </si>
+  <si>
+    <t>Canta aleluya</t>
+  </si>
+  <si>
+    <t>Como un águila</t>
+  </si>
+  <si>
+    <t>Con el alma</t>
+  </si>
+  <si>
+    <t>Ebenu shalom</t>
+  </si>
+  <si>
+    <t>El saludo del cristiano</t>
+  </si>
+  <si>
+    <t>Entonces la virgen</t>
+  </si>
+  <si>
+    <t>La fiesta de los vencedores</t>
+  </si>
+  <si>
+    <t>Oh jehová señor nuestro</t>
+  </si>
+  <si>
+    <t>Para ti oh jehová</t>
+  </si>
+  <si>
+    <t>Regocíjate Sion</t>
+  </si>
+  <si>
+    <t>Sacude el polvo</t>
+  </si>
+  <si>
+    <t>Tu vienes contra mi</t>
+  </si>
+  <si>
+    <t>Un pentecostés pedimos hoy</t>
+  </si>
+  <si>
+    <t>Una cosa yo se</t>
+  </si>
+  <si>
+    <t>Yo subiré</t>
+  </si>
+  <si>
+    <t>Refugio de liberación</t>
+  </si>
+  <si>
+    <t>Si-</t>
+  </si>
+  <si>
+    <t>La paloma celestial</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>Aleluya</t>
+  </si>
+  <si>
+    <t>Comprado con sangre por cristo             vals</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Escogido fui de Dios            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(corrido)</t>
+    </r>
+  </si>
+  <si>
+    <t>Oh cuanto amo a cristo                             vals </t>
+  </si>
+  <si>
+    <t>Porque él vive</t>
+  </si>
+  <si>
+    <t>Solo creed</t>
+  </si>
+  <si>
+    <t>Heme aquí</t>
+  </si>
+  <si>
+    <t>Jesús yo te amo</t>
+  </si>
+  <si>
+    <t>Si tu hablas con Dios</t>
+  </si>
+  <si>
+    <t>Toma mi mente</t>
+  </si>
+  <si>
+    <t>Yo sé que Jesús me ama de verdad</t>
+  </si>
+  <si>
+    <t>Caminare este sendero</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -948,6 +1673,24 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -975,7 +1718,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -998,11 +1741,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1042,6 +1813,24 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1377,15 +2166,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFFAD3AD-3141-4DD4-85D5-8961B77DBF3E}">
-  <dimension ref="A1:C267"/>
+  <dimension ref="A1:J392"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="42.28515625" customWidth="1"/>
+    <col min="5" max="5" width="39.7109375" customWidth="1"/>
+    <col min="6" max="6" width="27.85546875" customWidth="1"/>
+    <col min="7" max="7" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1395,8 +2187,14 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -1406,8 +2204,14 @@
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -1417,8 +2221,14 @@
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E3" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1428,8 +2238,14 @@
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E4" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1439,8 +2255,14 @@
       <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -1450,8 +2272,14 @@
       <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -1461,8 +2289,14 @@
       <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E7" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
@@ -1472,8 +2306,14 @@
       <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E8" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -1483,8 +2323,14 @@
       <c r="C9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E9" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -1494,8 +2340,14 @@
       <c r="C10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E10" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
@@ -1505,8 +2357,14 @@
       <c r="C11" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E11" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
@@ -1516,8 +2374,17 @@
       <c r="C12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="J12" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
@@ -1527,8 +2394,14 @@
       <c r="C13" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E13" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>21</v>
       </c>
@@ -1538,8 +2411,14 @@
       <c r="C14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E14" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>22</v>
       </c>
@@ -1549,8 +2428,14 @@
       <c r="C15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E15" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>23</v>
       </c>
@@ -1560,8 +2445,14 @@
       <c r="C16" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>24</v>
       </c>
@@ -1571,8 +2462,14 @@
       <c r="C17" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="14" t="s">
+        <v>495</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>26</v>
       </c>
@@ -1582,8 +2479,14 @@
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E18" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
@@ -1593,8 +2496,14 @@
       <c r="C19" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E19" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
@@ -1604,8 +2513,14 @@
       <c r="C20" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E20" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>30</v>
       </c>
@@ -1615,8 +2530,14 @@
       <c r="C21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E21" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>31</v>
       </c>
@@ -1626,8 +2547,14 @@
       <c r="C22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E22" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>33</v>
       </c>
@@ -1637,8 +2564,14 @@
       <c r="C23" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E23" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>34</v>
       </c>
@@ -1648,8 +2581,14 @@
       <c r="C24" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E24" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>35</v>
       </c>
@@ -1659,8 +2598,14 @@
       <c r="C25" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E25" s="14" t="s">
+        <v>496</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>36</v>
       </c>
@@ -1670,8 +2615,14 @@
       <c r="C26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E26" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>37</v>
       </c>
@@ -1681,8 +2632,14 @@
       <c r="C27" s="8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E27" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
@@ -1692,8 +2649,14 @@
       <c r="C28" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E28" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>40</v>
       </c>
@@ -1703,8 +2666,14 @@
       <c r="C29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E29" s="14" t="s">
+        <v>469</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>41</v>
       </c>
@@ -1714,8 +2683,14 @@
       <c r="C30" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E30" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>42</v>
       </c>
@@ -1725,8 +2700,14 @@
       <c r="C31" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E31" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>43</v>
       </c>
@@ -1736,8 +2717,14 @@
       <c r="C32" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E32" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>44</v>
       </c>
@@ -1747,8 +2734,14 @@
       <c r="C33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E33" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>45</v>
       </c>
@@ -1758,8 +2751,14 @@
       <c r="C34" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E34" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>46</v>
       </c>
@@ -1769,8 +2768,14 @@
       <c r="C35" s="3" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E35" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>47</v>
       </c>
@@ -1780,8 +2785,14 @@
       <c r="C36" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E36" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>48</v>
       </c>
@@ -1791,8 +2802,14 @@
       <c r="C37" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E37" s="14" t="s">
+        <v>527</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>49</v>
       </c>
@@ -1802,8 +2819,14 @@
       <c r="C38" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E38" s="14" t="s">
+        <v>497</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>51</v>
       </c>
@@ -1813,8 +2836,14 @@
       <c r="C39" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E39" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>52</v>
       </c>
@@ -1824,8 +2853,14 @@
       <c r="C40" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E40" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>53</v>
       </c>
@@ -1835,8 +2870,14 @@
       <c r="C41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E41" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>54</v>
       </c>
@@ -1846,8 +2887,14 @@
       <c r="C42" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E42" s="16" t="s">
+        <v>498</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>55</v>
       </c>
@@ -1857,8 +2904,14 @@
       <c r="C43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E43" s="16" t="s">
+        <v>517</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>56</v>
       </c>
@@ -1868,8 +2921,14 @@
       <c r="C44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E44" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>57</v>
       </c>
@@ -1879,8 +2938,14 @@
       <c r="C45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E45" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>58</v>
       </c>
@@ -1890,8 +2955,14 @@
       <c r="C46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E46" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>59</v>
       </c>
@@ -1901,8 +2972,14 @@
       <c r="C47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E47" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F47" s="18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>60</v>
       </c>
@@ -1912,8 +2989,14 @@
       <c r="C48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E48" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="F48" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
         <v>61</v>
       </c>
@@ -1923,8 +3006,14 @@
       <c r="C49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E49" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>62</v>
       </c>
@@ -1934,8 +3023,14 @@
       <c r="C50" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E50" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F50" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>63</v>
       </c>
@@ -1945,8 +3040,14 @@
       <c r="C51" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E51" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>64</v>
       </c>
@@ -1956,8 +3057,14 @@
       <c r="C52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E52" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F52" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>65</v>
       </c>
@@ -1967,8 +3074,14 @@
       <c r="C53" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E53" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F53" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>66</v>
       </c>
@@ -1978,8 +3091,14 @@
       <c r="C54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E54" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>67</v>
       </c>
@@ -1989,8 +3108,14 @@
       <c r="C55" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E55" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F55" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>69</v>
       </c>
@@ -2000,8 +3125,14 @@
       <c r="C56" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E56" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="F56" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>70</v>
       </c>
@@ -2011,8 +3142,14 @@
       <c r="C57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E57" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>71</v>
       </c>
@@ -2022,8 +3159,14 @@
       <c r="C58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E58" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>73</v>
       </c>
@@ -2033,8 +3176,14 @@
       <c r="C59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E59" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="F59" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>74</v>
       </c>
@@ -2044,8 +3193,14 @@
       <c r="C60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E60" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F60" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>75</v>
       </c>
@@ -2055,8 +3210,14 @@
       <c r="C61" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E61" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>77</v>
       </c>
@@ -2066,8 +3227,14 @@
       <c r="C62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E62" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F62" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>78</v>
       </c>
@@ -2077,8 +3244,14 @@
       <c r="C63" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E63" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="F63" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>79</v>
       </c>
@@ -2088,8 +3261,14 @@
       <c r="C64" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E64" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="F64" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>80</v>
       </c>
@@ -2099,8 +3278,14 @@
       <c r="C65" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E65" s="17" t="s">
+        <v>444</v>
+      </c>
+      <c r="F65" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>81</v>
       </c>
@@ -2110,8 +3295,14 @@
       <c r="C66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E66" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F66" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>82</v>
       </c>
@@ -2121,8 +3312,14 @@
       <c r="C67" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E67" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="F67" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>83</v>
       </c>
@@ -2132,8 +3329,14 @@
       <c r="C68" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E68" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="F68" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>84</v>
       </c>
@@ -2143,8 +3346,14 @@
       <c r="C69" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E69" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="F69" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>86</v>
       </c>
@@ -2154,8 +3363,14 @@
       <c r="C70" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E70" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="F70" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
         <v>87</v>
       </c>
@@ -2165,8 +3380,14 @@
       <c r="C71" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E71" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="F71" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>88</v>
       </c>
@@ -2176,8 +3397,14 @@
       <c r="C72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E72" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F72" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>89</v>
       </c>
@@ -2187,8 +3414,14 @@
       <c r="C73" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E73" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>90</v>
       </c>
@@ -2198,8 +3431,14 @@
       <c r="C74" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E74" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="F74" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>91</v>
       </c>
@@ -2209,8 +3448,14 @@
       <c r="C75" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E75" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F75" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>92</v>
       </c>
@@ -2220,8 +3465,14 @@
       <c r="C76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E76" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="F76" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>93</v>
       </c>
@@ -2231,8 +3482,14 @@
       <c r="C77" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E77" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F77" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>94</v>
       </c>
@@ -2242,8 +3499,14 @@
       <c r="C78" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E78" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F78" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>95</v>
       </c>
@@ -2253,8 +3516,14 @@
       <c r="C79" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E79" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F79" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>96</v>
       </c>
@@ -2264,8 +3533,14 @@
       <c r="C80" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E80" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="F80" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>98</v>
       </c>
@@ -2275,8 +3550,14 @@
       <c r="C81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E81" s="16" t="s">
+        <v>339</v>
+      </c>
+      <c r="F81" s="18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="10" t="s">
         <v>99</v>
       </c>
@@ -2286,8 +3567,14 @@
       <c r="C82" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E82" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="F82" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>100</v>
       </c>
@@ -2297,8 +3584,14 @@
       <c r="C83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E83" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="F83" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>101</v>
       </c>
@@ -2308,8 +3601,14 @@
       <c r="C84" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E84" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="F84" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>102</v>
       </c>
@@ -2319,8 +3618,14 @@
       <c r="C85" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E85" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="F85" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>103</v>
       </c>
@@ -2330,8 +3635,14 @@
       <c r="C86" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E86" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="F86" s="18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>104</v>
       </c>
@@ -2341,8 +3652,14 @@
       <c r="C87" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E87" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="F87" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>105</v>
       </c>
@@ -2352,8 +3669,14 @@
       <c r="C88" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E88" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F88" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>106</v>
       </c>
@@ -2363,8 +3686,14 @@
       <c r="C89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E89" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="F89" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>107</v>
       </c>
@@ -2374,8 +3703,14 @@
       <c r="C90" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E90" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="F90" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>108</v>
       </c>
@@ -2385,8 +3720,14 @@
       <c r="C91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E91" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="F91" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>109</v>
       </c>
@@ -2396,8 +3737,14 @@
       <c r="C92" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E92" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="F92" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>110</v>
       </c>
@@ -2407,8 +3754,14 @@
       <c r="C93" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E93" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F93" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>111</v>
       </c>
@@ -2418,8 +3771,14 @@
       <c r="C94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E94" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F94" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>112</v>
       </c>
@@ -2429,8 +3788,14 @@
       <c r="C95" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E95" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F95" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>113</v>
       </c>
@@ -2440,8 +3805,14 @@
       <c r="C96" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E96" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="F96" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="11" t="s">
         <v>114</v>
       </c>
@@ -2451,8 +3822,14 @@
       <c r="C97" s="13" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E97" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="F97" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>115</v>
       </c>
@@ -2462,8 +3839,14 @@
       <c r="C98" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E98" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="F98" s="18" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>116</v>
       </c>
@@ -2473,8 +3856,14 @@
       <c r="C99" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E99" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F99" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>117</v>
       </c>
@@ -2484,8 +3873,14 @@
       <c r="C100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E100" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="F100" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>118</v>
       </c>
@@ -2495,8 +3890,14 @@
       <c r="C101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E101" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F101" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>119</v>
       </c>
@@ -2506,8 +3907,14 @@
       <c r="C102" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E102" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="F102" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>120</v>
       </c>
@@ -2517,8 +3924,14 @@
       <c r="C103" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E103" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="F103" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>121</v>
       </c>
@@ -2528,8 +3941,14 @@
       <c r="C104" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E104" s="17" t="s">
+        <v>382</v>
+      </c>
+      <c r="F104" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>122</v>
       </c>
@@ -2539,8 +3958,14 @@
       <c r="C105" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E105" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="F105" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>123</v>
       </c>
@@ -2550,8 +3975,14 @@
       <c r="C106" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E106" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F106" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>124</v>
       </c>
@@ -2561,8 +3992,14 @@
       <c r="C107" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E107" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F107" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>125</v>
       </c>
@@ -2572,8 +4009,14 @@
       <c r="C108" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E108" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="F108" s="15" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>126</v>
       </c>
@@ -2583,8 +4026,14 @@
       <c r="C109" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E109" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="F109" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>127</v>
       </c>
@@ -2594,8 +4043,14 @@
       <c r="C110" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E110" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="F110" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>128</v>
       </c>
@@ -2605,8 +4060,14 @@
       <c r="C111" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E111" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F111" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>129</v>
       </c>
@@ -2616,8 +4077,14 @@
       <c r="C112" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E112" s="16" t="s">
+        <v>501</v>
+      </c>
+      <c r="F112" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>131</v>
       </c>
@@ -2627,8 +4094,14 @@
       <c r="C113" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E113" s="16" t="s">
+        <v>501</v>
+      </c>
+      <c r="F113" s="15" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>132</v>
       </c>
@@ -2638,8 +4111,14 @@
       <c r="C114" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E114" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F114" s="15" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>133</v>
       </c>
@@ -2649,8 +4128,14 @@
       <c r="C115" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E115" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F115" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>134</v>
       </c>
@@ -2660,8 +4145,14 @@
       <c r="C116" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E116" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F116" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>135</v>
       </c>
@@ -2671,8 +4162,14 @@
       <c r="C117" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E117" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F117" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>136</v>
       </c>
@@ -2682,8 +4179,14 @@
       <c r="C118" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E118" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="F118" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>137</v>
       </c>
@@ -2693,8 +4196,14 @@
       <c r="C119" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E119" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F119" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>138</v>
       </c>
@@ -2704,8 +4213,14 @@
       <c r="C120" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E120" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="F120" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>139</v>
       </c>
@@ -2715,8 +4230,14 @@
       <c r="C121" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E121" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="F121" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>140</v>
       </c>
@@ -2726,8 +4247,14 @@
       <c r="C122" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E122" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="F122" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>141</v>
       </c>
@@ -2737,8 +4264,14 @@
       <c r="C123" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E123" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="F123" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>142</v>
       </c>
@@ -2748,8 +4281,14 @@
       <c r="C124" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E124" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="F124" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>143</v>
       </c>
@@ -2759,8 +4298,14 @@
       <c r="C125" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E125" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="F125" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>144</v>
       </c>
@@ -2770,8 +4315,14 @@
       <c r="C126" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E126" s="17" t="s">
+        <v>445</v>
+      </c>
+      <c r="F126" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>145</v>
       </c>
@@ -2781,8 +4332,14 @@
       <c r="C127" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E127" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="F127" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>146</v>
       </c>
@@ -2792,8 +4349,14 @@
       <c r="C128" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E128" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F128" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>147</v>
       </c>
@@ -2803,8 +4366,14 @@
       <c r="C129" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E129" s="16" t="s">
+        <v>502</v>
+      </c>
+      <c r="F129" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>148</v>
       </c>
@@ -2814,8 +4383,14 @@
       <c r="C130" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E130" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="F130" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
         <v>149</v>
       </c>
@@ -2825,8 +4400,14 @@
       <c r="C131" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E131" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="F131" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>150</v>
       </c>
@@ -2836,8 +4417,14 @@
       <c r="C132" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E132" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="F132" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>151</v>
       </c>
@@ -2847,8 +4434,14 @@
       <c r="C133" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E133" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="F133" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>152</v>
       </c>
@@ -2858,8 +4451,14 @@
       <c r="C134" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E134" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="F134" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
         <v>153</v>
       </c>
@@ -2869,8 +4468,14 @@
       <c r="C135" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E135" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="F135" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>154</v>
       </c>
@@ -2880,8 +4485,14 @@
       <c r="C136" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E136" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="F136" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
         <v>155</v>
       </c>
@@ -2891,8 +4502,14 @@
       <c r="C137" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E137" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="F137" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>156</v>
       </c>
@@ -2902,8 +4519,14 @@
       <c r="C138" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E138" s="16" t="s">
+        <v>518</v>
+      </c>
+      <c r="F138" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>157</v>
       </c>
@@ -2913,8 +4536,14 @@
       <c r="C139" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E139" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="F139" s="18" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>158</v>
       </c>
@@ -2924,8 +4553,14 @@
       <c r="C140" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E140" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="F140" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
         <v>159</v>
       </c>
@@ -2935,8 +4570,14 @@
       <c r="C141" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E141" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="F141" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>160</v>
       </c>
@@ -2946,8 +4587,14 @@
       <c r="C142" s="3" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E142" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="F142" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>162</v>
       </c>
@@ -2957,8 +4604,14 @@
       <c r="C143" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E143" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="F143" s="18" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>163</v>
       </c>
@@ -2968,8 +4621,14 @@
       <c r="C144" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E144" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="F144" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>164</v>
       </c>
@@ -2979,8 +4638,14 @@
       <c r="C145" s="3" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E145" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="F145" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>165</v>
       </c>
@@ -2990,8 +4655,14 @@
       <c r="C146" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E146" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="F146" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>166</v>
       </c>
@@ -3001,8 +4672,14 @@
       <c r="C147" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E147" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="F147" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>167</v>
       </c>
@@ -3012,8 +4689,14 @@
       <c r="C148" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E148" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="F148" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>168</v>
       </c>
@@ -3023,8 +4706,14 @@
       <c r="C149" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E149" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="F149" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>169</v>
       </c>
@@ -3034,8 +4723,14 @@
       <c r="C150" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E150" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="F150" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>170</v>
       </c>
@@ -3045,8 +4740,14 @@
       <c r="C151" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E151" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="F151" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>171</v>
       </c>
@@ -3056,8 +4757,14 @@
       <c r="C152" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E152" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="F152" s="18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>172</v>
       </c>
@@ -3067,8 +4774,14 @@
       <c r="C153" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E153" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="F153" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>173</v>
       </c>
@@ -3078,8 +4791,14 @@
       <c r="C154" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E154" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="F154" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>174</v>
       </c>
@@ -3089,8 +4808,14 @@
       <c r="C155" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E155" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="F155" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>175</v>
       </c>
@@ -3100,8 +4825,14 @@
       <c r="C156" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E156" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="F156" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>176</v>
       </c>
@@ -3111,8 +4842,14 @@
       <c r="C157" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E157" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="F157" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>177</v>
       </c>
@@ -3122,8 +4859,14 @@
       <c r="C158" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E158" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="F158" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
         <v>178</v>
       </c>
@@ -3133,8 +4876,14 @@
       <c r="C159" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E159" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="F159" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
         <v>179</v>
       </c>
@@ -3144,8 +4893,14 @@
       <c r="C160" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E160" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="F160" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>180</v>
       </c>
@@ -3155,8 +4910,14 @@
       <c r="C161" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E161" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="F161" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>181</v>
       </c>
@@ -3166,8 +4927,14 @@
       <c r="C162" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E162" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="F162" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>182</v>
       </c>
@@ -3177,8 +4944,14 @@
       <c r="C163" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E163" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="F163" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>183</v>
       </c>
@@ -3188,8 +4961,14 @@
       <c r="C164" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E164" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="F164" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>184</v>
       </c>
@@ -3199,8 +4978,14 @@
       <c r="C165" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E165" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="F165" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>185</v>
       </c>
@@ -3210,8 +4995,14 @@
       <c r="C166" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E166" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="F166" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>186</v>
       </c>
@@ -3221,8 +5012,14 @@
       <c r="C167" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E167" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="F167" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>187</v>
       </c>
@@ -3232,8 +5029,14 @@
       <c r="C168" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E168" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="F168" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>188</v>
       </c>
@@ -3243,8 +5046,14 @@
       <c r="C169" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E169" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="F169" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>189</v>
       </c>
@@ -3254,8 +5063,14 @@
       <c r="C170" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E170" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="F170" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>190</v>
       </c>
@@ -3265,8 +5080,14 @@
       <c r="C171" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E171" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="F171" s="15" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>191</v>
       </c>
@@ -3276,8 +5097,14 @@
       <c r="C172" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E172" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="F172" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>192</v>
       </c>
@@ -3287,8 +5114,14 @@
       <c r="C173" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E173" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="F173" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
         <v>193</v>
       </c>
@@ -3298,8 +5131,14 @@
       <c r="C174" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E174" s="16" t="s">
+        <v>522</v>
+      </c>
+      <c r="F174" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
         <v>194</v>
       </c>
@@ -3309,8 +5148,14 @@
       <c r="C175" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E175" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="F175" s="15" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
         <v>195</v>
       </c>
@@ -3320,8 +5165,14 @@
       <c r="C176" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E176" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="F176" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>196</v>
       </c>
@@ -3331,8 +5182,14 @@
       <c r="C177" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E177" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="F177" s="15" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>197</v>
       </c>
@@ -3342,8 +5199,14 @@
       <c r="C178" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E178" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="F178" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>199</v>
       </c>
@@ -3353,8 +5216,14 @@
       <c r="C179" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E179" s="16" t="s">
+        <v>523</v>
+      </c>
+      <c r="F179" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>200</v>
       </c>
@@ -3364,8 +5233,14 @@
       <c r="C180" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E180" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="F180" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>201</v>
       </c>
@@ -3375,8 +5250,14 @@
       <c r="C181" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E181" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="F181" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>202</v>
       </c>
@@ -3386,8 +5267,14 @@
       <c r="C182" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E182" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="F182" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>203</v>
       </c>
@@ -3397,8 +5284,14 @@
       <c r="C183" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E183" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="F183" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>204</v>
       </c>
@@ -3408,8 +5301,14 @@
       <c r="C184" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E184" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="F184" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>205</v>
       </c>
@@ -3419,8 +5318,14 @@
       <c r="C185" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E185" s="16" t="s">
+        <v>503</v>
+      </c>
+      <c r="F185" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>206</v>
       </c>
@@ -3430,8 +5335,14 @@
       <c r="C186" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E186" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="F186" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>207</v>
       </c>
@@ -3441,8 +5352,14 @@
       <c r="C187" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E187" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="F187" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>208</v>
       </c>
@@ -3452,8 +5369,14 @@
       <c r="C188" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E188" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="F188" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>209</v>
       </c>
@@ -3463,8 +5386,14 @@
       <c r="C189" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E189" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="F189" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>210</v>
       </c>
@@ -3474,8 +5403,14 @@
       <c r="C190" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E190" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="F190" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
         <v>211</v>
       </c>
@@ -3485,8 +5420,14 @@
       <c r="C191" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E191" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="F191" s="15" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>212</v>
       </c>
@@ -3496,8 +5437,14 @@
       <c r="C192" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E192" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="F192" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>213</v>
       </c>
@@ -3507,8 +5454,14 @@
       <c r="C193" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E193" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="F193" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
         <v>214</v>
       </c>
@@ -3518,8 +5471,14 @@
       <c r="C194" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E194" s="17" t="s">
+        <v>460</v>
+      </c>
+      <c r="F194" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>215</v>
       </c>
@@ -3529,8 +5488,14 @@
       <c r="C195" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E195" s="16" t="s">
+        <v>346</v>
+      </c>
+      <c r="F195" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
         <v>216</v>
       </c>
@@ -3540,8 +5505,14 @@
       <c r="C196" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E196" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="F196" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>217</v>
       </c>
@@ -3551,8 +5522,14 @@
       <c r="C197" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E197" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="F197" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
         <v>218</v>
       </c>
@@ -3562,8 +5539,14 @@
       <c r="C198" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E198" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="F198" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
         <v>219</v>
       </c>
@@ -3573,8 +5556,14 @@
       <c r="C199" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E199" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="F199" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
         <v>220</v>
       </c>
@@ -3584,8 +5573,14 @@
       <c r="C200" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E200" s="17" t="s">
+        <v>448</v>
+      </c>
+      <c r="F200" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>221</v>
       </c>
@@ -3595,8 +5590,14 @@
       <c r="C201" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E201" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="F201" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
         <v>222</v>
       </c>
@@ -3606,8 +5607,14 @@
       <c r="C202" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E202" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="F202" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>223</v>
       </c>
@@ -3617,8 +5624,14 @@
       <c r="C203" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E203" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="F203" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>224</v>
       </c>
@@ -3628,8 +5641,14 @@
       <c r="C204" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E204" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="F204" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
         <v>225</v>
       </c>
@@ -3639,8 +5658,14 @@
       <c r="C205" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E205" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="F205" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
         <v>226</v>
       </c>
@@ -3650,8 +5675,14 @@
       <c r="C206" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E206" s="17" t="s">
+        <v>449</v>
+      </c>
+      <c r="F206" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
         <v>227</v>
       </c>
@@ -3661,8 +5692,14 @@
       <c r="C207" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E207" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F207" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
         <v>228</v>
       </c>
@@ -3672,8 +5709,14 @@
       <c r="C208" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E208" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="F208" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>229</v>
       </c>
@@ -3683,8 +5726,14 @@
       <c r="C209" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E209" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="F209" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
         <v>230</v>
       </c>
@@ -3694,8 +5743,14 @@
       <c r="C210" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E210" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F210" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
         <v>231</v>
       </c>
@@ -3705,8 +5760,14 @@
       <c r="C211" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E211" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="F211" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
         <v>232</v>
       </c>
@@ -3716,8 +5777,14 @@
       <c r="C212" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E212" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="F212" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
         <v>233</v>
       </c>
@@ -3727,8 +5794,14 @@
       <c r="C213" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E213" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="F213" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
         <v>235</v>
       </c>
@@ -3738,8 +5811,14 @@
       <c r="C214" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E214" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="F214" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
         <v>236</v>
       </c>
@@ -3749,8 +5828,14 @@
       <c r="C215" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E215" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="F215" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
         <v>237</v>
       </c>
@@ -3760,8 +5845,14 @@
       <c r="C216" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E216" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="F216" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
         <v>238</v>
       </c>
@@ -3771,8 +5862,14 @@
       <c r="C217" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E217" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="F217" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
         <v>239</v>
       </c>
@@ -3782,8 +5879,14 @@
       <c r="C218" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E218" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F218" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
         <v>240</v>
       </c>
@@ -3793,8 +5896,14 @@
       <c r="C219" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E219" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="F219" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
         <v>241</v>
       </c>
@@ -3804,8 +5913,14 @@
       <c r="C220" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E220" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="F220" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>242</v>
       </c>
@@ -3815,8 +5930,14 @@
       <c r="C221" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E221" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="F221" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
         <v>243</v>
       </c>
@@ -3826,8 +5947,14 @@
       <c r="C222" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E222" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="F222" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
         <v>244</v>
       </c>
@@ -3837,8 +5964,14 @@
       <c r="C223" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E223" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F223" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
         <v>245</v>
       </c>
@@ -3848,8 +5981,14 @@
       <c r="C224" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E224" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="F224" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
         <v>246</v>
       </c>
@@ -3859,8 +5998,14 @@
       <c r="C225" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E225" s="16" t="s">
+        <v>519</v>
+      </c>
+      <c r="F225" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
         <v>247</v>
       </c>
@@ -3870,8 +6015,14 @@
       <c r="C226" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E226" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="F226" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
         <v>248</v>
       </c>
@@ -3881,8 +6032,14 @@
       <c r="C227" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E227" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="F227" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>249</v>
       </c>
@@ -3892,8 +6049,14 @@
       <c r="C228" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="229" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E228" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="F228" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
         <v>250</v>
       </c>
@@ -3903,8 +6066,14 @@
       <c r="C229" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E229" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="F229" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
         <v>251</v>
       </c>
@@ -3914,8 +6083,14 @@
       <c r="C230" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="231" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E230" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="F230" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>252</v>
       </c>
@@ -3925,8 +6100,14 @@
       <c r="C231" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="232" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E231" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="F231" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
         <v>253</v>
       </c>
@@ -3936,8 +6117,14 @@
       <c r="C232" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E232" s="16" t="s">
+        <v>505</v>
+      </c>
+      <c r="F232" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
         <v>254</v>
       </c>
@@ -3947,8 +6134,14 @@
       <c r="C233" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="234" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E233" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="F233" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
         <v>255</v>
       </c>
@@ -3958,8 +6151,14 @@
       <c r="C234" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="235" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E234" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="F234" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
         <v>256</v>
       </c>
@@ -3969,8 +6168,14 @@
       <c r="C235" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="236" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E235" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="F235" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
         <v>257</v>
       </c>
@@ -3980,8 +6185,14 @@
       <c r="C236" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="237" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E236" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="F236" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
         <v>258</v>
       </c>
@@ -3991,8 +6202,14 @@
       <c r="C237" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="238" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E237" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="F237" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
         <v>259</v>
       </c>
@@ -4002,8 +6219,14 @@
       <c r="C238" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="239" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E238" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="F238" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
         <v>260</v>
       </c>
@@ -4013,8 +6236,14 @@
       <c r="C239" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="240" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E239" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="F239" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
         <v>261</v>
       </c>
@@ -4024,8 +6253,14 @@
       <c r="C240" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="241" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E240" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="F240" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
         <v>262</v>
       </c>
@@ -4035,8 +6270,14 @@
       <c r="C241" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="242" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E241" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="F241" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
         <v>263</v>
       </c>
@@ -4046,8 +6287,14 @@
       <c r="C242" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="243" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E242" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="F242" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
         <v>264</v>
       </c>
@@ -4057,8 +6304,14 @@
       <c r="C243" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="244" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E243" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="F243" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
         <v>265</v>
       </c>
@@ -4068,8 +6321,14 @@
       <c r="C244" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="245" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E244" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="F244" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
         <v>266</v>
       </c>
@@ -4079,8 +6338,14 @@
       <c r="C245" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="246" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E245" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="F245" s="18" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
         <v>267</v>
       </c>
@@ -4090,8 +6355,14 @@
       <c r="C246" s="3" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="247" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E246" s="17" t="s">
+        <v>451</v>
+      </c>
+      <c r="F246" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
         <v>268</v>
       </c>
@@ -4101,8 +6372,14 @@
       <c r="C247" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="248" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E247" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="F247" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
         <v>269</v>
       </c>
@@ -4112,8 +6389,14 @@
       <c r="C248" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="249" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E248" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="F248" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
         <v>270</v>
       </c>
@@ -4123,8 +6406,14 @@
       <c r="C249" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="250" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E249" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="F249" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
         <v>271</v>
       </c>
@@ -4134,8 +6423,14 @@
       <c r="C250" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="251" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E250" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="F250" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
         <v>272</v>
       </c>
@@ -4145,8 +6440,14 @@
       <c r="C251" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="252" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E251" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="F251" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="3" t="s">
         <v>273</v>
       </c>
@@ -4156,8 +6457,14 @@
       <c r="C252" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="253" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E252" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="F252" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
         <v>274</v>
       </c>
@@ -4167,8 +6474,14 @@
       <c r="C253" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="254" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E253" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="F253" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
         <v>275</v>
       </c>
@@ -4178,8 +6491,14 @@
       <c r="C254" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="255" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E254" s="16" t="s">
+        <v>507</v>
+      </c>
+      <c r="F254" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
         <v>276</v>
       </c>
@@ -4189,8 +6508,14 @@
       <c r="C255" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="256" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E255" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="F255" s="15" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="3" t="s">
         <v>277</v>
       </c>
@@ -4200,8 +6525,14 @@
       <c r="C256" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="257" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E256" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="F256" s="15" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
         <v>278</v>
       </c>
@@ -4211,8 +6542,14 @@
       <c r="C257" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="258" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E257" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F257" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="3" t="s">
         <v>279</v>
       </c>
@@ -4222,8 +6559,14 @@
       <c r="C258" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="259" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E258" s="16" t="s">
+        <v>494</v>
+      </c>
+      <c r="F258" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
         <v>280</v>
       </c>
@@ -4233,8 +6576,14 @@
       <c r="C259" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="260" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E259" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="F259" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="3" t="s">
         <v>281</v>
       </c>
@@ -4244,8 +6593,14 @@
       <c r="C260" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="261" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E260" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="F260" s="18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
         <v>282</v>
       </c>
@@ -4255,8 +6610,14 @@
       <c r="C261" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="262" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E261" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="F261" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
         <v>283</v>
       </c>
@@ -4266,8 +6627,14 @@
       <c r="C262" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="263" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E262" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="F262" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
         <v>284</v>
       </c>
@@ -4277,8 +6644,14 @@
       <c r="C263" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="264" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E263" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="F263" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
         <v>285</v>
       </c>
@@ -4288,8 +6661,14 @@
       <c r="C264" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="265" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E264" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="F264" s="18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
         <v>286</v>
       </c>
@@ -4299,8 +6678,14 @@
       <c r="C265" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="266" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E265" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="F265" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
         <v>287</v>
       </c>
@@ -4310,8 +6695,14 @@
       <c r="C266" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="267" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E266" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="F266" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
         <v>288</v>
       </c>
@@ -4321,8 +6712,654 @@
       <c r="C267" s="3" t="s">
         <v>289</v>
       </c>
-    </row>
+      <c r="E267" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="F267" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E268" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="F268" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E269" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="F269" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E270" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="F270" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E271" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="F271" s="18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E272" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="F272" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="273" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E273" s="16" t="s">
+        <v>524</v>
+      </c>
+      <c r="F273" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="274" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E274" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="F274" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="275" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E275" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="F275" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="276" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E276" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="F276" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="277" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E277" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="F277" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="278" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E278" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="F278" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="279" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E279" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="F279" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="280" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E280" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="F280" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="281" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E281" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="F281" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="282" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E282" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="F282" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="283" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E283" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="F283" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="284" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E284" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="F284" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="285" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E285" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="F285" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="286" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E286" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="F286" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="287" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E287" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="F287" s="18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="288" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E288" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="F288" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="289" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E289" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="F289" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="290" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E290" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="F290" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="291" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E291" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="F291" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="292" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E292" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="F292" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="293" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E293" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="F293" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="294" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E294" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="F294" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="295" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E295" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="F295" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="296" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E296" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="F296" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="297" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E297" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="F297" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="298" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E298" s="16" t="s">
+        <v>487</v>
+      </c>
+      <c r="F298" s="15" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="299" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E299" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="F299" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="300" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E300" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="F300" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="301" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E301" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="F301" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="302" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E302" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="F302" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="303" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E303" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="F303" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="304" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E304" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="F304" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="305" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E305" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="F305" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="306" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E306" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="F306" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="307" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E307" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="F307" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="308" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E308" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="F308" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="309" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E309" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="F309" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="310" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E310" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="F310" s="18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="311" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E311" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="F311" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="312" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E312" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="F312" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="313" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E313" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="F313" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="314" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E314" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="F314" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="315" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E315" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="F315" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E316" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="F316" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="317" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E317" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="F317" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="318" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E318" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="F318" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="319" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E319" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="F319" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="320" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E320" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="F320" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="321" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E321" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="F321" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="322" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E322" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="F322" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="323" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E323" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="F323" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="324" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E324" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="F324" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="325" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E325" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="F325" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="326" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E326" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="F326" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="327" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E327" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="F327" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="328" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E328" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="F328" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="329" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E329" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="F329" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="330" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E330" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="F330" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="331" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E331" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="F331" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="332" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E332" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="F332" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="333" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E333" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="F333" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="334" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E334" s="17" t="s">
+        <v>452</v>
+      </c>
+      <c r="F334" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="335" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E335" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="F335" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="336" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E336" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="F336" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="337" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E337" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="F337" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="338" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E338" s="16" t="s">
+        <v>526</v>
+      </c>
+      <c r="F338" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="339" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E339" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="F339" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="340" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E340" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="F340" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="341" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E341" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="F341" s="15" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="342" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E342" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="F342" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="343" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E343" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="F343" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="344" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E344" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="F344" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="345" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E345" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="F345" s="15" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="346" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E346" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="F346" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="347" spans="5:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E1:F395">
+    <sortCondition ref="E1:E395"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
